--- a/RESULTS/tables/shap_feature_importance.xlsx
+++ b/RESULTS/tables/shap_feature_importance.xlsx
@@ -448,76 +448,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BW_diff_seq</t>
+          <t>六個月內住院次數</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Body Weight Change</t>
+          <t>Hospitalizations within 6 Months</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1178761318516569</v>
+        <v>0.09948165319490121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>六個月內住院次數</t>
+          <t>ADL_diff_seq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hospitalizations within 6 Months</t>
+          <t>ADL Change</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09956966293309966</v>
+        <v>0.08739074936720574</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADL_last_score</t>
+          <t>BW_diff_seq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADL Last Score</t>
+          <t>Body Weight Change</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09589493368233533</v>
+        <v>0.06519801945346609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADL_Min</t>
+          <t>ADL_last_score</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADL Minimum</t>
+          <t>ADL Last Score</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01405451623337394</v>
+        <v>0.0439645521853179</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADL_std</t>
+          <t>ADL_總分_max</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADL Standard Deviation</t>
+          <t>ADL Total Max</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01301743712981954</v>
+        <v>0.01667834811898785</v>
       </c>
     </row>
     <row r="7">
@@ -532,82 +532,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0102828644874362</v>
+        <v>0.008861556583820953</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BW_last</t>
+          <t>ADL_Max</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Body Weight (Last)</t>
+          <t>ADL Maximum</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.009951971275919406</v>
+        <v>0.008046724174853897</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BW_first</t>
+          <t>ADL_std</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Body Weight (First)</t>
+          <t>ADL Standard Deviation</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.009803706654134632</v>
+        <v>0.006663062217657525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADL_總分_max</t>
+          <t>BW_first</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADL Total Max</t>
+          <t>Body Weight (First)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006262880036469215</v>
+        <v>0.00474479815075919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>first_ 意識總分</t>
+          <t>使用呼吸輔具</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Consciousness Score (First)</t>
+          <t>Use of Respiratory Aid</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004780067410834682</v>
+        <v>0.004159931835406121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>使用呼吸輔具</t>
+          <t>BW_last</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Use of Respiratory Aid</t>
+          <t>Body Weight (Last)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003977981974050262</v>
+        <v>0.003112863848084312</v>
       </c>
     </row>
     <row r="13">
@@ -622,262 +622,262 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00265787222460953</v>
+        <v>0.002431726269343627</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADL_first_score</t>
+          <t>預估年齡</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ADL First Score</t>
+          <t>Estimated Age</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002256902398496329</v>
+        <v>0.001527332298300533</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>意識總分_diff</t>
+          <t>ADL_first_score</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Consciousness Score Difference</t>
+          <t>ADL First Score</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001949908042696722</v>
+        <v>0.001168374916467935</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>預估年齡</t>
+          <t>ADL_Min</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Estimated Age</t>
+          <t>ADL Minimum</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001592379992121435</v>
+        <v>0.0006837702833292627</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>diff_has_feeding_tube</t>
+          <t>意識總分_diff</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Feeding Tube Change</t>
+          <t>Consciousness Score Difference</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0007761190454966496</v>
+        <v>0.0006777294040660306</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ADL_Max</t>
+          <t>last_has_feeding_tube</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADL Maximum</t>
+          <t>Has Feeding Tube (Last)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0006344743406788104</v>
+        <v>0.0006413074930225297</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ADL_明顯惡化</t>
+          <t>first_has_feeding_tube</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADL Significant Deterioration</t>
+          <t>Has Feeding Tube (First)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00051897711751803</v>
+        <v>0.0005630092988201918</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>last_ 意識總分</t>
+          <t>diff_has_feeding_tube</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Consciousness Score (Last)</t>
+          <t>Feeding Tube Change</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005061557550437284</v>
+        <v>0.0005478428737097962</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>diff_has_denture</t>
+          <t>意識總分Max</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Denture Change</t>
+          <t>Consciousness Score Max</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004901961765428286</v>
+        <v>0.0005369138697163436</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>意識總分Max</t>
+          <t>first_has_denture</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Consciousness Score Max</t>
+          <t>Has Denture (First)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004591364743708895</v>
+        <v>0.0005162391676477739</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>had_fall</t>
+          <t>diff_has_denture</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Had Fall</t>
+          <t>Denture Change</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004418457561471401</v>
+        <v>0.0005018082744499686</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>first_has_denture</t>
+          <t>ADL_明顯惡化</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Has Denture (First)</t>
+          <t>ADL Significant Deterioration</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004053726947335392</v>
+        <v>0.0005007644751162425</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ADL_last_CouldNot</t>
+          <t>first_ 意識總分</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADL Last Could Not Perform</t>
+          <t>Consciousness Score (First)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004053020621188781</v>
+        <v>0.0004357186324779657</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>last_has_feeding_tube</t>
+          <t>last_has_denture</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Has Feeding Tube (Last)</t>
+          <t>Has Denture (Last)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003224649208641197</v>
+        <v>0.0004313073242535192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>first_has_feeding_tube</t>
+          <t>ADL_first_CouldNot</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Has Feeding Tube (First)</t>
+          <t>ADL First Could Not Perform</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003196708314227529</v>
+        <v>0.0004197274562470308</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>last_has_denture</t>
+          <t>ADL_last_CouldNot</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Has Denture (Last)</t>
+          <t>ADL Last Could Not Perform</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.000307865217003213</v>
+        <v>0.0003941421175611174</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ADL_diff_seq</t>
+          <t>had_fall</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ADL Change</t>
+          <t>Had Fall</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.000306639474639036</v>
+        <v>0.0002595302726678596</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ADL_first_CouldNot</t>
+          <t>last_ 意識總分</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADL First Could Not Perform</t>
+          <t>Consciousness Score (Last)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.000301182144975665</v>
+        <v>0.0002434066746920863</v>
       </c>
     </row>
   </sheetData>
